--- a/cds_files/OklahomaState_CDS_2022-2023.xlsx
+++ b/cds_files/OklahomaState_CDS_2022-2023.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.89</v>
+        <v>0.908</v>
       </c>
       <c r="C3" t="n">
-        <v>0.45</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.11</v>
+        <v>0.092</v>
       </c>
       <c r="C4" t="n">
-        <v>0.55</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
     </row>
   </sheetData>
